--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -7172,16 +7172,16 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O41" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.520544093281193</v>
+        <v>1.524216905100713</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O42" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8570,16 +8570,16 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O49" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.612364388769188</v>
+        <v>1.619710012408228</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O50" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -9510,16 +9510,16 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O54" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.3048433810201426</v>
+        <v>0.3525899346738999</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O55" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>674327</v>
+        <v>674343</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -1544,28 +1544,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1632,17 +1646,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1676,25 +1690,39 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.2803464128485004</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1702,6 +1730,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN8" t="b">
+        <v>1</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1719,7 +1805,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -1732,42 +1818,42 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1880,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1843,98 +1929,26 @@
       <c r="O9" t="n">
         <v>30</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2803464128485004</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Hepatit B</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -2028,17 +2042,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2063,34 +2077,48 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>466</v>
+        <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>466</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.711530307896222</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>30</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Hepatit B</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -2098,9 +2126,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
+        <v>1</v>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2110,12 +2196,12 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT10" t="n">
@@ -2123,47 +2209,47 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2281,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2234,84 +2320,98 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>130</v>
+        <v>466</v>
       </c>
       <c r="O11" t="n">
-        <v>130</v>
+        <v>466</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.443193997023468</v>
+        <v>1.711530307896222</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2443,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2382,98 +2482,84 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>96310</v>
+        <v>130</v>
       </c>
       <c r="O12" t="n">
-        <v>96310</v>
+        <v>130</v>
       </c>
       <c r="Q12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>6.816408781247707</v>
+        <v>1.443193997023468</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -2505,12 +2591,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2544,84 +2630,98 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>96310</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>96310</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>6.816408781247707</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -2653,12 +2753,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2692,16 +2792,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.02906954885688069</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2734,42 +2834,42 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2901,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2840,16 +2940,16 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01891260466471829</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2882,42 +2982,42 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -2949,12 +3049,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2988,16 +3088,16 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2803464128485004</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3006,7 +3106,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -3031,7 +3131,7 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
@@ -3044,42 +3144,42 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3211,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3150,29 +3250,29 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Hepatit B</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -3182,7 +3282,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -3197,7 +3297,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3232,17 +3332,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -3265,7 +3365,7 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
@@ -3278,42 +3378,42 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3445,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3375,25 +3475,25 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>463</v>
+        <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>463</v>
+        <v>30</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.700511872437663</v>
+        <v>0.2803464128485004</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3402,7 +3502,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3412,7 +3512,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
@@ -3422,12 +3522,12 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -3435,47 +3535,47 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -3502,17 +3602,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3537,93 +3637,179 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>117</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.298874597321121</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Hepatit B</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -3655,12 +3841,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3694,16 +3880,16 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>123191</v>
+        <v>463</v>
       </c>
       <c r="O20" t="n">
-        <v>123191</v>
+        <v>463</v>
       </c>
       <c r="Q20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>8.718930683944413</v>
+        <v>1.700511872437663</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3712,7 +3898,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3737,7 +3923,7 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT20" t="n">
@@ -3750,42 +3936,42 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3817,12 +4003,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3856,16 +4042,16 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.298874597321121</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -3898,42 +4084,42 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -3965,12 +4151,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4004,84 +4190,98 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>27</v>
+        <v>123191</v>
       </c>
       <c r="O22" t="n">
-        <v>27</v>
+        <v>123191</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R22" t="n">
-        <v>0.05232518794238524</v>
+        <v>8.718930683944413</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4313,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4194,42 +4394,42 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4261,12 +4461,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4300,98 +4500,84 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="O24" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3831400975596171</v>
+        <v>0.05232518794238524</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -4418,17 +4604,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4462,39 +4648,25 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>41</v>
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Hepatit B</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4502,64 +4674,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN25" t="b">
-        <v>1</v>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4577,7 +4691,7 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
@@ -4590,42 +4704,42 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4652,17 +4766,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4687,34 +4801,48 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>423</v>
-      </c>
-      <c r="Q26" t="n">
         <v>0</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.553599399656871</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4722,9 +4850,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN26" t="b">
+        <v>1</v>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
@@ -4734,12 +4920,12 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
@@ -4747,47 +4933,47 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4819,12 +5005,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4849,93 +5035,107 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="O27" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.076844751625203</v>
+        <v>0.3831400975596171</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -4962,17 +5162,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4997,34 +5197,48 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>114147</v>
+        <v>41</v>
       </c>
       <c r="O28" t="n">
-        <v>114147</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>28</v>
-      </c>
-      <c r="R28" t="n">
-        <v>8.078835148510873</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>41</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Hepatit B</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -5032,9 +5246,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN28" t="b">
+        <v>1</v>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
@@ -5044,12 +5316,12 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5057,47 +5329,47 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -5129,12 +5401,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5168,84 +5440,98 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.553599399656871</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5563,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5316,16 +5602,16 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="O30" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0465112781710091</v>
+        <v>1.076844751625203</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -5358,42 +5644,42 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5711,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5464,59 +5750,73 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>114147</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>114147</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>0.09456302332359146</v>
+        <v>8.078835148510873</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -5526,22 +5826,22 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -5573,12 +5873,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5612,98 +5912,84 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3924849779879006</v>
+        <v>0</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5730,17 +6016,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5774,170 +6060,84 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O33" t="n">
-        <v>42</v>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Hepatit B</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN33" t="b">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.0465112781710091</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -5969,12 +6169,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5999,25 +6199,25 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.836405909759895</v>
+        <v>0.09456302332359146</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -6026,7 +6226,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -6036,7 +6236,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
@@ -6046,12 +6246,12 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -6059,47 +6259,47 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6126,17 +6326,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6161,34 +6361,48 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>111588</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
-        <v>111588</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>35</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7.897720102604809</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -6196,9 +6410,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
@@ -6208,12 +6480,12 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
@@ -6221,22 +6493,22 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -6246,22 +6518,22 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6565,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6323,93 +6595,107 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01355270280196709</v>
+        <v>0.3924849779879006</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -6436,17 +6722,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6471,93 +6757,179 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="O37" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.03488345862825683</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Hepatit B</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -6589,12 +6961,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6628,84 +7000,98 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.836405909759895</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -6737,12 +7123,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6776,16 +7162,16 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>42</v>
+        <v>111588</v>
       </c>
       <c r="O39" t="n">
-        <v>42</v>
+        <v>111588</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="R39" t="n">
-        <v>0.3924849779879006</v>
+        <v>7.897720102604809</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -6794,7 +7180,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6804,7 +7190,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
@@ -6814,12 +7200,12 @@
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT39" t="n">
@@ -6827,47 +7213,47 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -6894,17 +7280,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6938,170 +7324,84 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>42</v>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Hepatit B</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN40" t="b">
         <v>1</v>
       </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7133,12 +7433,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7163,107 +7463,93 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>415</v>
+        <v>18</v>
       </c>
       <c r="O41" t="n">
-        <v>415</v>
+        <v>18</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.524216905100713</v>
+        <v>0.03488345862825683</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7290,17 +7576,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7325,48 +7611,34 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>415</v>
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Hepatitis B (unspecified)</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -7374,67 +7646,9 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN42" t="b">
-        <v>1</v>
-      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
@@ -7444,12 +7658,12 @@
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
@@ -7457,47 +7671,47 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7524,17 +7738,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7559,34 +7773,48 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>115796</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>115796</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>28</v>
-      </c>
-      <c r="R43" t="n">
-        <v>8.195544296888791</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -7594,9 +7822,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
@@ -7606,12 +7892,12 @@
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
@@ -7619,22 +7905,22 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -7644,22 +7930,22 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7691,12 +7977,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7721,93 +8007,107 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.3924849779879006</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -7834,17 +8134,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7869,93 +8169,179 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="O45" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.04263533832342501</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Hepatit B</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -7987,12 +8373,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -8026,84 +8412,98 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>415</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>415</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.07565041865887316</v>
+        <v>1.524216905100713</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8130,17 +8530,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8174,25 +8574,39 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>25</v>
+        <v>415</v>
       </c>
       <c r="O47" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.2336220107070837</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>415</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -8200,9 +8614,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
@@ -8212,12 +8684,12 @@
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -8225,47 +8697,47 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8292,17 +8764,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -8336,39 +8808,25 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>25</v>
+        <v>115796</v>
       </c>
       <c r="O48" t="n">
-        <v>25</v>
+        <v>115796</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>28</v>
+      </c>
+      <c r="R48" t="n">
+        <v>8.195544296888791</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Hepatit B</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -8376,67 +8834,9 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN48" t="b">
-        <v>1</v>
-      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
@@ -8446,12 +8846,12 @@
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT48" t="n">
@@ -8459,47 +8859,47 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -8531,12 +8931,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8561,107 +8961,93 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.619710012408228</v>
+        <v>0</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8688,17 +9074,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8723,179 +9109,93 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>441</v>
+        <v>22</v>
       </c>
       <c r="O50" t="n">
-        <v>441</v>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>Hepatitis B (unspecified)</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN50" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.04263533832342501</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8927,12 +9227,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8957,93 +9257,107 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O51" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.04263533832342501</v>
+        <v>0.07565041865887316</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9070,17 +9384,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -9105,34 +9419,48 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="O52" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.2896912932767837</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -9140,6 +9468,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN52" t="b">
+        <v>1</v>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -9157,7 +9543,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -9170,42 +9556,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9618,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -9267,112 +9653,40 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="O53" t="n">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.2336220107070837</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>Hepatit B</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG53" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN53" t="b">
-        <v>1</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -9466,17 +9780,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -9501,34 +9815,48 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="O54" t="n">
-        <v>96</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0.3525899346738999</v>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>25</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Hepatit B</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -9536,9 +9864,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
@@ -9548,12 +9934,12 @@
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -9561,47 +9947,47 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -9628,7 +10014,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -9663,112 +10049,40 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>96</v>
+        <v>441</v>
       </c>
       <c r="O55" t="n">
-        <v>96</v>
+        <v>441</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.619710012408228</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>Hepatitis B (unspecified)</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN55" t="b">
-        <v>1</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -9862,126 +10176,1300 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>441</v>
+      </c>
+      <c r="O56" t="n">
+        <v>441</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>D008</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>乙型肝炎</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>22</v>
+      </c>
+      <c r="O57" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.04263533832342501</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>31</v>
+      </c>
+      <c r="O58" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.2896912932767837</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>31</v>
+      </c>
+      <c r="O59" t="n">
+        <v>31</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Hepatit B</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N56" t="n">
+      <c r="N60" t="n">
+        <v>151</v>
+      </c>
+      <c r="O60" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.5545945847474882</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT60" t="n">
         <v>1</v>
       </c>
-      <c r="O56" t="n">
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>151</v>
+      </c>
+      <c r="O61" t="n">
+        <v>151</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN61" t="b">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
         <v>0</v>
       </c>
-      <c r="R56" t="n">
+      <c r="R62" t="n">
         <v>0.001937969923792046</v>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP56" t="inlineStr">
+      <c r="AP62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR56" t="inlineStr">
+      <c r="AR62" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS56" t="inlineStr"/>
-      <c r="AT56" t="n">
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
+      <c r="AU62" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV56" t="inlineStr">
+      <c r="AV62" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW56" t="inlineStr">
+      <c r="AW62" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
+      <c r="AX62" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr">
+      <c r="AY62" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA56" t="inlineStr">
+      <c r="BA62" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB56" t="inlineStr">
+      <c r="BB62" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC56" t="inlineStr">
+      <c r="BC62" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -10113,7 +11601,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
@@ -10133,7 +11621,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -10143,7 +11631,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -10165,7 +11653,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>674343</v>
+        <v>674398</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -10058,16 +10058,16 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O55" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.619710012408228</v>
+        <v>1.623382824227747</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O56" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -10998,16 +10998,16 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="O60" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.5545945847474882</v>
+        <v>0.5178664665522904</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -11160,10 +11160,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="O61" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -11394,16 +11394,16 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>674398</v>
+        <v>674390</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -927,9 +927,6 @@
       <c r="O3" t="n">
         <v>113</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>1.254468628181937</v>
       </c>
@@ -1237,9 +1234,6 @@
       <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -1385,9 +1379,6 @@
       <c r="O6" t="n">
         <v>12</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.02325563908550455</v>
       </c>
@@ -1782,7 +1773,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -1929,9 +1920,6 @@
       <c r="O9" t="n">
         <v>30</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.2803464128485004</v>
       </c>
@@ -2487,9 +2475,6 @@
       <c r="O12" t="n">
         <v>130</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>1.443193997023468</v>
       </c>
@@ -2797,9 +2782,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2945,9 +2927,6 @@
       <c r="O15" t="n">
         <v>15</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.02906954885688069</v>
       </c>
@@ -3342,7 +3321,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -3489,9 +3468,6 @@
       <c r="O18" t="n">
         <v>30</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.2803464128485004</v>
       </c>
@@ -4047,9 +4023,6 @@
       <c r="O21" t="n">
         <v>117</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>1.298874597321121</v>
       </c>
@@ -4357,9 +4330,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4505,9 +4475,6 @@
       <c r="O24" t="n">
         <v>27</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.05232518794238524</v>
       </c>
@@ -4902,7 +4869,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5049,9 +5016,6 @@
       <c r="O27" t="n">
         <v>41</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.3831400975596171</v>
       </c>
@@ -5445,9 +5409,6 @@
       <c r="O29" t="n">
         <v>423</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>1.553599399656871</v>
       </c>
@@ -5607,9 +5568,6 @@
       <c r="O30" t="n">
         <v>97</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>1.076844751625203</v>
       </c>
@@ -5917,9 +5875,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6065,9 +6020,6 @@
       <c r="O33" t="n">
         <v>24</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.0465112781710091</v>
       </c>
@@ -6213,9 +6165,6 @@
       <c r="O34" t="n">
         <v>5</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.09456302332359146</v>
       </c>
@@ -6462,7 +6411,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -6609,9 +6558,6 @@
       <c r="O36" t="n">
         <v>42</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.3924849779879006</v>
       </c>
@@ -7005,9 +6951,6 @@
       <c r="O38" t="n">
         <v>500</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>1.836405909759895</v>
       </c>
@@ -7329,9 +7272,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -7477,9 +7417,6 @@
       <c r="O41" t="n">
         <v>18</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.03488345862825683</v>
       </c>
@@ -7625,9 +7562,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7874,7 +7808,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -8021,9 +7955,6 @@
       <c r="O44" t="n">
         <v>42</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.3924849779879006</v>
       </c>
@@ -8417,9 +8348,6 @@
       <c r="O46" t="n">
         <v>415</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>1.524216905100713</v>
       </c>
@@ -8975,9 +8903,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9123,9 +9048,6 @@
       <c r="O50" t="n">
         <v>22</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.04263533832342501</v>
       </c>
@@ -9271,9 +9193,6 @@
       <c r="O51" t="n">
         <v>4</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.07565041865887316</v>
       </c>
@@ -9520,7 +9439,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -9667,9 +9586,6 @@
       <c r="O53" t="n">
         <v>25</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.2336220107070837</v>
       </c>
@@ -10063,9 +9979,6 @@
       <c r="O55" t="n">
         <v>442</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>1.623382824227747</v>
       </c>
@@ -10459,9 +10372,6 @@
       <c r="O57" t="n">
         <v>22</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.04263533832342501</v>
       </c>
@@ -10602,16 +10512,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O58" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R58" t="n">
-        <v>0.2896912932767837</v>
+        <v>0.2803464128485004</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -10764,10 +10671,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O59" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -11003,9 +10910,6 @@
       <c r="O60" t="n">
         <v>141</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.5178664665522904</v>
       </c>
@@ -11398,9 +11302,6 @@
       </c>
       <c r="O62" t="n">
         <v>2</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0.003875939847584092</v>
@@ -11653,7 +11554,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>674390</v>
+        <v>674389</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -8343,13 +8343,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O46" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="R46" t="n">
-        <v>1.524216905100713</v>
+        <v>1.527889716920233</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O47" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -9974,13 +9974,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="O55" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="R55" t="n">
-        <v>1.623382824227747</v>
+        <v>1.634401259686306</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="O56" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -10905,13 +10905,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="O60" t="n">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="R60" t="n">
-        <v>0.5178664665522904</v>
+        <v>0.7272167402649184</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -11064,10 +11064,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="O61" t="n">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>674389</v>
+        <v>674450</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -8343,13 +8343,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O46" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="R46" t="n">
-        <v>1.527889716920233</v>
+        <v>1.531562528739753</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O47" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -10905,13 +10905,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="O60" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="R60" t="n">
-        <v>0.7272167402649184</v>
+        <v>0.7565992348210768</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -11064,10 +11064,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="O61" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>674450</v>
+        <v>674459</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -9974,13 +9974,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O55" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="R55" t="n">
-        <v>1.634401259686306</v>
+        <v>1.630728447866787</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O56" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -10905,13 +10905,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="O60" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="R60" t="n">
-        <v>0.7565992348210768</v>
+        <v>0.8337282830309923</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -11064,10 +11064,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="O61" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>674459</v>
+        <v>674479</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -8594,7 +8594,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -10328,12 +10328,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -10367,81 +10367,98 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>22</v>
+        <v>126727</v>
       </c>
       <c r="O57" t="n">
-        <v>22</v>
+        <v>126727</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>34</v>
       </c>
       <c r="R57" t="n">
-        <v>0.04263533832342501</v>
+        <v>8.969193600053766</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -10468,17 +10485,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -10512,22 +10529,39 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>30</v>
+        <v>126727</v>
       </c>
       <c r="O58" t="n">
-        <v>30</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.2803464128485004</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>126727</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>SRC_CN_CDC</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -10535,9 +10569,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>country:CN:national</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>China CDC hepatitis B series without a source-reported acute/chronic course split.</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN58" t="b">
+        <v>1</v>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
@@ -10547,12 +10639,12 @@
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -10560,47 +10652,47 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -10627,17 +10719,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -10671,170 +10763,81 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="O59" t="n">
-        <v>30</v>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Hepatit B</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN59" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.04263533832342501</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10866,12 +10869,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -10896,22 +10899,22 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="O60" t="n">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="R60" t="n">
-        <v>0.8337282830309923</v>
+        <v>0.2803464128485004</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -10920,7 +10923,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -10930,7 +10933,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
@@ -10940,12 +10943,12 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -10953,47 +10956,47 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11025,12 +11028,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -11055,38 +11058,38 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="O61" t="n">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Hepatitis B (unspecified)</t>
+          <t>Hepatit B</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -11096,7 +11099,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -11111,7 +11114,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -11126,7 +11129,7 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
@@ -11146,17 +11149,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -11164,7 +11167,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
@@ -11174,12 +11177,12 @@
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -11187,47 +11190,47 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11259,118 +11262,511 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>227</v>
+      </c>
+      <c r="O62" t="n">
+        <v>227</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.8337282830309923</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>227</v>
+      </c>
+      <c r="O63" t="n">
+        <v>227</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>D008</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>乙型肝炎</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N62" t="n">
+      <c r="N64" t="n">
         <v>2</v>
       </c>
-      <c r="O62" t="n">
+      <c r="O64" t="n">
         <v>2</v>
       </c>
-      <c r="R62" t="n">
+      <c r="R64" t="n">
         <v>0.003875939847584092</v>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO62" t="inlineStr">
+      <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP62" t="inlineStr">
+      <c r="AP64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR62" t="inlineStr">
+      <c r="AR64" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS62" t="inlineStr"/>
-      <c r="AT62" t="n">
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AU62" t="inlineStr">
+      <c r="AU64" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV62" t="inlineStr">
+      <c r="AV64" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW62" t="inlineStr">
+      <c r="AW64" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
+      <c r="AX64" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr">
+      <c r="AY64" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
+      <c r="AZ64" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA62" t="inlineStr">
+      <c r="BA64" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB62" t="inlineStr">
+      <c r="BB64" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC62" t="inlineStr">
+      <c r="BC64" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -11492,7 +11888,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -11502,7 +11898,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -11522,7 +11918,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -11532,7 +11928,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -11554,7 +11950,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>674479</v>
+        <v>801206</v>
       </c>
     </row>
     <row r="16">
@@ -11564,7 +11960,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>196</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -9974,13 +9974,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O55" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R55" t="n">
-        <v>1.630728447866787</v>
+        <v>1.634401259686306</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O56" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>801206</v>
+        <v>801207</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -9974,13 +9974,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O55" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="R55" t="n">
-        <v>1.634401259686306</v>
+        <v>1.638074071505826</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O56" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>801207</v>
+        <v>801208</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -9974,13 +9974,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O55" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="R55" t="n">
-        <v>1.638074071505826</v>
+        <v>1.641746883325346</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O56" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>801208</v>
+        <v>801209</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -8343,13 +8343,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O46" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R46" t="n">
-        <v>1.531562528739753</v>
+        <v>1.535235340559272</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O47" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -9188,13 +9188,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.07565041865887316</v>
+        <v>0</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -9974,13 +9974,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O55" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="R55" t="n">
-        <v>1.641746883325346</v>
+        <v>1.652765318783906</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O56" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -10908,13 +10908,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0.2803464128485004</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -10961,42 +10961,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -11067,29 +11067,29 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Hepatit B</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -11149,17 +11149,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -11195,42 +11195,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11262,12 +11262,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -11292,22 +11292,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>227</v>
+        <v>28</v>
       </c>
       <c r="O62" t="n">
-        <v>227</v>
+        <v>28</v>
       </c>
       <c r="R62" t="n">
-        <v>0.8337282830309923</v>
+        <v>0.2616566519919337</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -11349,47 +11349,47 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11421,12 +11421,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -11451,38 +11451,38 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>227</v>
+        <v>28</v>
       </c>
       <c r="O63" t="n">
-        <v>227</v>
+        <v>28</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Hepatitis B (unspecified)</t>
+          <t>Hepatit B</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr">
@@ -11542,17 +11542,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -11583,47 +11583,47 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11655,118 +11655,511 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>227</v>
+      </c>
+      <c r="O64" t="n">
+        <v>227</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.8337282830309923</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>227</v>
+      </c>
+      <c r="O65" t="n">
+        <v>227</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>D008</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>乙型肝炎</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N64" t="n">
-        <v>2</v>
-      </c>
-      <c r="O64" t="n">
-        <v>2</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0.003875939847584092</v>
-      </c>
-      <c r="S64" t="inlineStr">
+      <c r="N66" t="n">
+        <v>4</v>
+      </c>
+      <c r="O66" t="n">
+        <v>4</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.007751879695168184</v>
+      </c>
+      <c r="S66" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO64" t="inlineStr">
+      <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP64" t="inlineStr">
+      <c r="AP66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR64" t="inlineStr">
+      <c r="AR66" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS64" t="inlineStr"/>
-      <c r="AT64" t="n">
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="AU64" t="inlineStr">
+      <c r="AU66" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV64" t="inlineStr">
+      <c r="AV66" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW64" t="inlineStr">
+      <c r="AW66" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr">
+      <c r="AY66" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA64" t="inlineStr">
+      <c r="BA66" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB64" t="inlineStr">
+      <c r="BB66" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC64" t="inlineStr">
+      <c r="BC66" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -11888,7 +12281,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -11898,7 +12291,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -11918,7 +12311,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -11950,7 +12343,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>801209</v>
+        <v>801210</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -9974,13 +9974,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O55" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R55" t="n">
-        <v>1.652765318783906</v>
+        <v>1.656438130603425</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O56" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>801210</v>
+        <v>801211</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -10724,12 +10724,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -10763,13 +10763,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.04263533832342501</v>
+        <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -10802,42 +10802,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -10908,95 +10908,81 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="R60" t="n">
-        <v>0.01891260466471829</v>
+        <v>0.04263533832342501</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11023,7 +11009,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11072,98 +11058,23 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
+      <c r="R61" t="n">
+        <v>0.01891260466471829</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN61" t="b">
-        <v>1</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -11257,17 +11168,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -11301,22 +11212,39 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>28</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.2616566519919337</v>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -11324,6 +11252,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN62" t="b">
+        <v>1</v>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -11341,7 +11327,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -11354,42 +11340,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11402,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11465,98 +11451,23 @@
       <c r="O63" t="n">
         <v>28</v>
       </c>
+      <c r="R63" t="n">
+        <v>0.2616566519919337</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Hepatit B</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN63" t="b">
-        <v>1</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -11650,17 +11561,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -11685,31 +11596,48 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>227</v>
+        <v>28</v>
       </c>
       <c r="O64" t="n">
-        <v>227</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0.8337282830309923</v>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>28</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Hepatit B</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -11717,9 +11645,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN64" t="b">
+        <v>1</v>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
@@ -11729,12 +11715,12 @@
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -11742,47 +11728,47 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11795,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -11858,98 +11844,23 @@
       <c r="O65" t="n">
         <v>227</v>
       </c>
+      <c r="R65" t="n">
+        <v>0.8337282830309923</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Hepatitis B (unspecified)</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN65" t="b">
-        <v>1</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -12043,123 +11954,357 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>227</v>
+      </c>
+      <c r="O66" t="n">
+        <v>227</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>D008</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>乙型肝炎</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N66" t="n">
-        <v>4</v>
-      </c>
-      <c r="O66" t="n">
-        <v>4</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.007751879695168184</v>
-      </c>
-      <c r="S66" t="inlineStr">
+      <c r="N67" t="n">
+        <v>9</v>
+      </c>
+      <c r="O67" t="n">
+        <v>9</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.01744172931412841</v>
+      </c>
+      <c r="S67" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO66" t="inlineStr">
+      <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP66" t="inlineStr">
+      <c r="AP67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR66" t="inlineStr">
+      <c r="AR67" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS66" t="inlineStr"/>
-      <c r="AT66" t="n">
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
         <v>0</v>
       </c>
-      <c r="AU66" t="inlineStr">
+      <c r="AU67" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV66" t="inlineStr">
+      <c r="AV67" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW66" t="inlineStr">
+      <c r="AW67" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
+      <c r="AX67" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY66" t="inlineStr">
+      <c r="AY67" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
+      <c r="AZ67" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA66" t="inlineStr">
+      <c r="BA67" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB66" t="inlineStr">
+      <c r="BB67" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC66" t="inlineStr">
+      <c r="BC67" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -12281,7 +12426,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -12291,7 +12436,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -12343,7 +12488,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>801211</v>
+        <v>801216</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -38361,13 +38361,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O209" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="R209" t="n">
-        <v>0.1799677791564697</v>
+        <v>0.3305530637567811</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -38520,10 +38520,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O210" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1184743</v>
+        <v>1184784</v>
       </c>
     </row>
     <row r="16">
